--- a/backend/data/financials_by_company/002354.SZ.xlsx
+++ b/backend/data/financials_by_company/002354.SZ.xlsx
@@ -3974,197 +3974,197 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
         </is>
       </c>
       <c r="EN1" t="inlineStr">
@@ -4259,28 +4259,28 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>7.73</v>
+        <v>10.34</v>
       </c>
       <c r="T2" t="n">
-        <v>7.15</v>
+        <v>8.23</v>
       </c>
       <c r="U2" t="n">
-        <v>8.09</v>
+        <v>9.31</v>
       </c>
       <c r="V2" t="n">
-        <v>8.5</v>
+        <v>10.32</v>
       </c>
       <c r="W2" t="n">
-        <v>7.73</v>
+        <v>10.34</v>
       </c>
       <c r="X2" t="n">
-        <v>7.15</v>
+        <v>8.23</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.09</v>
+        <v>9.31</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.5</v>
+        <v>10.32</v>
       </c>
       <c r="AA2" t="n">
         <v>1530489600</v>
@@ -4289,31 +4289,31 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.652</v>
+        <v>0.607</v>
       </c>
       <c r="AD2" t="n">
-        <v>170</v>
+        <v>187.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>288717634</v>
+        <v>618935090</v>
       </c>
       <c r="AF2" t="n">
-        <v>288717634</v>
+        <v>618935090</v>
       </c>
       <c r="AG2" t="n">
-        <v>154330762</v>
+        <v>210838723</v>
       </c>
       <c r="AH2" t="n">
-        <v>338763367</v>
+        <v>403682713</v>
       </c>
       <c r="AI2" t="n">
-        <v>338763367</v>
+        <v>403682713</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8.5</v>
+        <v>9.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -4322,16 +4322,16 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>14063979520</v>
+        <v>15503469568</v>
       </c>
       <c r="AO2" t="n">
-        <v>12789948388</v>
+        <v>15553106708</v>
       </c>
       <c r="AP2" t="n">
         <v>5.36</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.869999999999999</v>
+        <v>10.34</v>
       </c>
       <c r="AR2" t="n">
         <v>125.2</v>
@@ -4340,13 +4340,13 @@
         <v>1.64</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.5747576</v>
+        <v>7.247703</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.5588</v>
+        <v>7.1428</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.70035</v>
+        <v>6.77335</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>13654509568</v>
+        <v>15093998592</v>
       </c>
       <c r="BB2" t="n">
         <v>-0.01115</v>
@@ -4387,7 +4387,7 @@
         <v>0.831</v>
       </c>
       <c r="BI2" t="n">
-        <v>10.228641</v>
+        <v>11.275572</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
@@ -4411,16 +4411,16 @@
         <v>0.05</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.383</v>
+        <v>7.056</v>
       </c>
       <c r="BR2" t="n">
-        <v>268.171</v>
+        <v>296.443</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.2840532</v>
+        <v>0.6597111</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BU2" t="n">
         <v>0.02</v>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>8.5</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -4538,148 +4538,148 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DB2" t="n">
-        <v>1782111840</v>
-      </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DD2" t="n">
+        <v>1783062261</v>
+      </c>
+      <c r="DE2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>finmb_261221062</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DG2" t="n">
+      <c r="DI2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DI2" t="b">
+      <c r="DK2" t="b">
         <v>0</v>
       </c>
-      <c r="DJ2" t="n">
-        <v>9.96119</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>8.5</v>
-      </c>
       <c r="DL2" t="inlineStr">
         <is>
+          <t>TIANYU DIGITAL TECH GP CO LTD</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
           <t>Tianyu Digital Technology Group Co.,Ltd.</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>8.09 - 8.5</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-9.381047000000001</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1265679000000</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.97000027</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>9.31 - 10.32</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DP2" t="n">
-        <v>154330762</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>3.1399999</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.5858208499999999</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>5.36 - 8.87</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.3699999</v>
-      </c>
       <c r="DU2" t="n">
-        <v>-0.04171363</v>
+        <v>210838723</v>
       </c>
       <c r="DV2" t="n">
-        <v>28.405321</v>
+        <v>4.0099998</v>
       </c>
       <c r="DW2" t="n">
+        <v>0.7481342600000001</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>5.36 - 10.34</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.97000027</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.09381047000000001</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>65.971115</v>
+      </c>
+      <c r="EB2" t="n">
         <v>1619780340</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EC2" t="n">
         <v>1619780340</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="ED2" t="n">
         <v>-0.01</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EE2" t="n">
         <v>0.05</v>
       </c>
-      <c r="EA2" t="n">
-        <v>1.9411998</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.29596874</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1.7996502</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.26859048</v>
-      </c>
-      <c r="EE2" t="n">
+      <c r="EF2" t="n">
+        <v>2.2272</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.3118105</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>2.5966501</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.38336277</v>
+      </c>
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="EF2" t="n">
+      <c r="EK2" t="n">
         <v>15</v>
       </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>TIANYU DIGITAL TECH GP CO LTD</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>Dalian Zeus Entertainment Co., Ltd.</t>
         </is>
       </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>1265679000000</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.77</v>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
       </c>
       <c r="EN2" t="inlineStr"/>
     </row>
